--- a/qa/exitcel-qa-testcases.xlsx
+++ b/qa/exitcel-qa-testcases.xlsx
@@ -98,11 +98,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -183,7 +183,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>274</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7">
@@ -193,7 +193,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -203,7 +203,7 @@
         </is>
       </c>
       <c r="B8" s="2">
-        <v>0.938</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="9">
@@ -213,7 +213,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -248,7 +248,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">29 / 30</t>
+          <t xml:space="preserve">30 / 30</t>
         </is>
       </c>
     </row>
@@ -308,7 +308,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 / 20</t>
+          <t xml:space="preserve">20 / 20</t>
         </is>
       </c>
     </row>
@@ -368,7 +368,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 / 12</t>
+          <t xml:space="preserve">12 / 12</t>
         </is>
       </c>
     </row>
@@ -380,7 +380,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 / 17</t>
+          <t xml:space="preserve">17 / 17</t>
         </is>
       </c>
     </row>
@@ -404,7 +404,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">21 / 25</t>
+          <t xml:space="preserve">25 / 25</t>
         </is>
       </c>
     </row>
@@ -416,7 +416,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 / 25</t>
+          <t xml:space="preserve">25 / 25</t>
         </is>
       </c>
     </row>
@@ -428,7 +428,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 / 19</t>
+          <t xml:space="preserve">18 / 19</t>
         </is>
       </c>
     </row>
@@ -440,7 +440,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">10 / 12</t>
+          <t xml:space="preserve">12 / 12</t>
         </is>
       </c>
     </row>
@@ -3300,9 +3300,9 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="F65" t="str">
+      <c r="F65" t="e">
         <f>MID("abcdef",0,2)</f>
-        <v>ab</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3311,12 +3311,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ab</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+          <t xml:space="preserve">#VALUE!</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -4558,10 +4558,10 @@
         <f>YEAR(DATE(2026,8,23))&amp;"/"&amp;MONTH(...)&amp;"/"&amp;DAY(...)</f>
         <v>#NAME?</v>
       </c>
-      <c r="G94" s="5">
+      <c r="G94" s="4">
         <v>46257</v>
       </c>
-      <c r="H94" s="5">
+      <c r="H94" s="4">
         <v>46257</v>
       </c>
       <c r="I94" s="3" t="inlineStr">
@@ -4808,17 +4808,17 @@
       </c>
       <c r="F100">
         <f>DAY(EDATE(DATE(2026,1,31),1))</f>
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G100">
         <v>28</v>
       </c>
       <c r="H100">
-        <v>3</v>
-      </c>
-      <c r="I100" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+        <v>28</v>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -4936,10 +4936,10 @@
         <f>HOUR(TIME(13,30,0))&amp;":"&amp;MINUTE(TIME(13,30,0))</f>
         <v>13:30</v>
       </c>
-      <c r="G103" s="6">
+      <c r="G103" s="5">
         <v>0.5625</v>
       </c>
-      <c r="H103" s="6">
+      <c r="H103" s="5">
         <v>0.5625</v>
       </c>
       <c r="I103" s="3" t="inlineStr">
@@ -5104,10 +5104,10 @@
         <f>TEXT(1234567,"#,##0")</f>
         <v>1,234,567</v>
       </c>
-      <c r="G107" s="7">
+      <c r="G107" s="6">
         <v>1234567</v>
       </c>
-      <c r="H107" s="7">
+      <c r="H107" s="6">
         <v>1234567</v>
       </c>
       <c r="I107" s="3" t="inlineStr">
@@ -5188,10 +5188,10 @@
         <f>TEXT(DATE(2026,8,5),"yyyy/mm/dd")</f>
         <v>2026/08/05</v>
       </c>
-      <c r="G109" s="5">
+      <c r="G109" s="4">
         <v>46239</v>
       </c>
-      <c r="H109" s="5">
+      <c r="H109" s="4">
         <v>46239</v>
       </c>
       <c r="I109" s="3" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">重複したまま(参照は1を指す)</t>
-        </is>
-      </c>
-      <c r="I140" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+          <t xml:space="preserve">一意化される</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -6823,10 +6823,10 @@
           <t xml:space="preserve">A1に ¥1,000 を入力</t>
         </is>
       </c>
-      <c r="G146" s="8">
+      <c r="G146" s="7">
         <v>1000</v>
       </c>
-      <c r="H146" s="8">
+      <c r="H146" s="7">
         <v>1000</v>
       </c>
       <c r="I146" s="3" t="inlineStr">
@@ -6866,10 +6866,10 @@
           <t xml:space="preserve">A1に 1,234 を入力</t>
         </is>
       </c>
-      <c r="G147" s="7">
+      <c r="G147" s="6">
         <v>1234</v>
       </c>
-      <c r="H147" s="7">
+      <c r="H147" s="6">
         <v>1234</v>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -6909,10 +6909,10 @@
           <t xml:space="preserve">A1に 2026/8/23 を入力</t>
         </is>
       </c>
-      <c r="G148" s="5">
+      <c r="G148" s="4">
         <v>46257</v>
       </c>
-      <c r="H148" s="5">
+      <c r="H148" s="4">
         <v>46257</v>
       </c>
       <c r="I148" s="3" t="inlineStr">
@@ -6952,10 +6952,10 @@
           <t xml:space="preserve">A1に 13:30 を入力</t>
         </is>
       </c>
-      <c r="G149" s="6">
+      <c r="G149" s="5">
         <v>0.5625</v>
       </c>
-      <c r="H149" s="6">
+      <c r="H149" s="5">
         <v>0.5625</v>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -7263,10 +7263,10 @@
           <t xml:space="preserve">A1に 2026/8/23 を入力し編集文字列を確認</t>
         </is>
       </c>
-      <c r="G156" s="5">
+      <c r="G156" s="4">
         <v>46257</v>
       </c>
-      <c r="H156" s="5">
+      <c r="H156" s="4">
         <v>46257</v>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -7306,10 +7306,10 @@
           <t xml:space="preserve">1234567 に #,##0 を適用</t>
         </is>
       </c>
-      <c r="G157" s="7">
+      <c r="G157" s="6">
         <v>1234567</v>
       </c>
-      <c r="H157" s="7">
+      <c r="H157" s="6">
         <v>1234567</v>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -7435,10 +7435,10 @@
           <t xml:space="preserve">1234 に ¥#,##0 を適用</t>
         </is>
       </c>
-      <c r="G160" s="8">
+      <c r="G160" s="7">
         <v>1234</v>
       </c>
-      <c r="H160" s="8">
+      <c r="H160" s="7">
         <v>1234</v>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -7564,10 +7564,10 @@
           <t xml:space="preserve">シリアル値に yyyy/mm/dd を適用</t>
         </is>
       </c>
-      <c r="G163" s="5">
+      <c r="G163" s="4">
         <v>46257</v>
       </c>
-      <c r="H163" s="5">
+      <c r="H163" s="4">
         <v>46257</v>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -8726,12 +8726,12 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">先頭がそのまま=で出力される</t>
-        </is>
-      </c>
-      <c r="I188" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+          <t xml:space="preserve">無害化されている</t>
+        </is>
+      </c>
+      <c r="I188" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5000ms以内(1455ms,末尾値OK)</t>
+          <t xml:space="preserve">5000ms以内(1436ms,末尾値OK)</t>
         </is>
       </c>
       <c r="I190" s="3" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000ms以内(57ms,5000行)</t>
+          <t xml:space="preserve">3000ms以内(54ms,5000行)</t>
         </is>
       </c>
       <c r="I192" s="3" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">10000ms以内(46ms,69KB)</t>
+          <t xml:space="preserve">10000ms以内(45ms,69KB)</t>
         </is>
       </c>
       <c r="I193" s="3" t="inlineStr">
@@ -9121,21 +9121,23 @@
           <t xml:space="preserve">C1:C2 と A1:A4</t>
         </is>
       </c>
-      <c r="F197">
+      <c r="F197" t="e">
         <f>SUMIFS(C1:C2,A1:A4,"x")</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
           <t xml:space="preserve">#VALUE!</t>
         </is>
       </c>
-      <c r="H197">
-        <v>2</v>
-      </c>
-      <c r="I197" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#VALUE!</t>
+        </is>
+      </c>
+      <c r="I197" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -9567,17 +9569,23 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="F207">
+      <c r="F207" t="e">
         <f>LEFT("abc",-1)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
           <t xml:space="preserve">#VALUE!</t>
         </is>
       </c>
-      <c r="I207" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#VALUE!</t>
+        </is>
+      </c>
+      <c r="I207" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -9925,10 +9933,10 @@
         <f>TEXT(TIME(9,5,0),"hh:mm")</f>
         <v>09:05</v>
       </c>
-      <c r="G215" s="6">
+      <c r="G215" s="5">
         <v>0.3784722222222222</v>
       </c>
-      <c r="H215" s="6">
+      <c r="H215" s="5">
         <v>0.3784722222222222</v>
       </c>
       <c r="I215" s="3" t="inlineStr">
@@ -10005,9 +10013,9 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="F217">
+      <c r="F217" t="e">
         <f>POWER(-8,1/3)</f>
-        <v>0</v>
+        <v>#NUM!</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -10016,12 +10024,12 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">NaN</t>
-        </is>
-      </c>
-      <c r="I217" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+          <t xml:space="preserve">#NUM!</t>
+        </is>
+      </c>
+      <c r="I217" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -10191,9 +10199,9 @@
       <c r="H221">
         <v>1000000000000</v>
       </c>
-      <c r="I221" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+      <c r="I221" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -10265,21 +10273,23 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="F223">
+      <c r="F223" t="e">
         <f>DATEDIF(DATE(2026,5,1),DATE(2026,1,1),"D")</f>
-        <v>-120</v>
+        <v>#NUM!</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
           <t xml:space="preserve">#NUM!</t>
         </is>
       </c>
-      <c r="H223">
-        <v>-120</v>
-      </c>
-      <c r="I223" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#NUM!</t>
+        </is>
+      </c>
+      <c r="I223" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -10353,17 +10363,17 @@
       </c>
       <c r="F225">
         <f>DAY(EDATE(DATE(2026,3,31),-1))</f>
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G225">
         <v>28</v>
       </c>
       <c r="H225">
-        <v>3</v>
-      </c>
-      <c r="I225" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+        <v>28</v>
+      </c>
+      <c r="I225" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -10445,7 +10455,7 @@
       <c r="H227">
         <v>2</v>
       </c>
-      <c r="I227" s="4" t="inlineStr">
+      <c r="I227" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">FAIL</t>
         </is>
@@ -11056,9 +11066,9 @@
       <c r="H241">
         <v>1e+21</v>
       </c>
-      <c r="I241" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+      <c r="I241" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -12075,10 +12085,10 @@
           <t xml:space="preserve">A1で桁区切りボタン</t>
         </is>
       </c>
-      <c r="G264" s="7">
+      <c r="G264" s="6">
         <v>1234567</v>
       </c>
-      <c r="H264" s="7">
+      <c r="H264" s="6">
         <v>1234567</v>
       </c>
       <c r="I264" s="3" t="inlineStr">
@@ -12442,7 +12452,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000ms以内(7ms)</t>
+          <t xml:space="preserve">2000ms以内(31ms)</t>
         </is>
       </c>
       <c r="I272" s="3" t="inlineStr">
@@ -12767,7 +12777,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">3枚(Sheet1,Sheet4,Sheet5)</t>
+          <t xml:space="preserve">3枚(Sheet1,Sheet2,Sheet3)</t>
         </is>
       </c>
       <c r="I279" s="3" t="inlineStr">
@@ -12854,10 +12864,10 @@
           <t xml:space="preserve">exportXlsx→importXlsx</t>
         </is>
       </c>
-      <c r="G281" s="5">
+      <c r="G281" s="4">
         <v>46257</v>
       </c>
-      <c r="H281" s="5">
+      <c r="H281" s="4">
         <v>46257</v>
       </c>
       <c r="I281" s="3" t="inlineStr">
@@ -12944,15 +12954,15 @@
           <t xml:space="preserve">B1に =EDATE(A1,1)</t>
         </is>
       </c>
-      <c r="G283" s="5">
+      <c r="G283" s="4">
         <v>46081</v>
       </c>
-      <c r="H283" s="5">
-        <v>46084</v>
-      </c>
-      <c r="I283" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+      <c r="H283" s="4">
+        <v>46081</v>
+      </c>
+      <c r="I283" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -12994,12 +13004,12 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">NaN</t>
-        </is>
-      </c>
-      <c r="I284" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+          <t xml:space="preserve">#NUM!</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -13016,7 +13026,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t xml:space="preserve">計算不能な結果が後続の集計を汚染しない</t>
+          <t xml:space="preserve">計算不能な結果が集計に黙って混入せずエラーとして伝播する</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13034,17 +13044,19 @@
           <t xml:space="preserve">A3に =SUM(A1:A2)</t>
         </is>
       </c>
-      <c r="G285">
-        <v>10</v>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#NUM!</t>
+        </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">NaN</t>
-        </is>
-      </c>
-      <c r="I285" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+          <t xml:space="preserve">#NUM!</t>
+        </is>
+      </c>
+      <c r="I285" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -13083,12 +13095,14 @@
           <t xml:space="preserve">#NUM!</t>
         </is>
       </c>
-      <c r="H286">
-        <v>-120</v>
-      </c>
-      <c r="I286" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#NUM!</t>
+        </is>
+      </c>
+      <c r="I286" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -13118,21 +13132,23 @@
           <t xml:space="preserve">A1:A4に条件, C1:C2に合計範囲</t>
         </is>
       </c>
-      <c r="F287">
+      <c r="F287" t="e">
         <f>SUMIFS(C1:C2,A1:A4,"x")</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
           <t xml:space="preserve">#VALUE!</t>
         </is>
       </c>
-      <c r="H287">
-        <v>2</v>
-      </c>
-      <c r="I287" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#VALUE!</t>
+        </is>
+      </c>
+      <c r="I287" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -13173,9 +13189,9 @@
       <c r="H288">
         <v>1.5</v>
       </c>
-      <c r="I288" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAIL</t>
+      <c r="I288" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13429,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -13526,7 +13542,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">起票済(未修正)</t>
+          <t xml:space="preserve">修正済(再テストPASS)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -13593,7 +13609,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">起票済(未修正)</t>
+          <t xml:space="preserve">修正済(再テストPASS)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -13660,7 +13676,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">起票済(未修正)</t>
+          <t xml:space="preserve">修正済(再テストPASS)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -13727,7 +13743,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">起票済(未修正)</t>
+          <t xml:space="preserve">修正済(再テストPASS)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -13792,7 +13808,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">起票済(未修正)</t>
+          <t xml:space="preserve">修正済(再テストPASS)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -13859,7 +13875,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">起票済(未修正)</t>
+          <t xml:space="preserve">修正済(再テストPASS)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -13926,7 +13942,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">起票済(未修正)</t>
+          <t xml:space="preserve">修正済(再テストPASS)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -13993,7 +14009,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">起票済(未修正)</t>
+          <t xml:space="preserve">修正済(再テストPASS)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -14059,7 +14075,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">起票済(未修正)</t>
+          <t xml:space="preserve">修正済(再テストPASS)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -14095,6 +14111,73 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">TC-H-028 / TC-H-048</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUG-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1900年3月1日より前の日付シリアルが Excel と1ずれる</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数式エンジン / 日付関数</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">軽微</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">低</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">起票済(対応保留・仕様として許容)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. A1 に =DATE(1900,1,1) を入力する / 2. A2 に =DATE(1900,3,1) を入力する / 3. それぞれの値を Excel の同じ数式と比べる</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Excel と同じ 1（1900/1/1）</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2（1900/3/1 以降は 61 で Excel と一致し、それ以前だけ1大きい）</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1900年1月1日〜2月28日の日付を xlsx でやり取りした場合にのみ1日ずれる。1900年3月1日以降は完全に一致するため、実運用で踏む可能性は極めて低い。</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Excel 側の既知の不具合。Excel は実在しない 1900年2月29日 をシリアル値60として数えるため、それ以前の日付のシリアル値が実際のカレンダーより1小さくなる。本実装は連続した実カレンダーで計算しており、数学的にはこちらが正しい。検証値: 1900/1/1 は実装2/Excel1、1900/2/28 は実装60/Excel59、1900/3/1 は双方61、1999/12/31 は双方36525。</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Excel 互換を優先するなら、シリアル値60を欠番として扱い、60未満のシリアル値に対してのみ1を減じる変換を serialToDate / dateToSerial に入れる。ただし正しいカレンダーをわざわざ壊す変更になるため、影響範囲(1900年の2か月弱)と天秤にかけて現時点では見送る。テストは既知の失敗としてベースラインに登録し、回帰検知の対象からは外している。</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-H-034</t>
         </is>
       </c>
     </row>
